--- a/Production/BOM_Hackpad_numeric_keypad.xlsx
+++ b/Production/BOM_Hackpad_numeric_keypad.xlsx
@@ -49,7 +49,7 @@
     <t>1N4148</t>
   </si>
   <si>
-    <t>D1,D2,D3,D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17</t>
+    <t>D2,D3,D4,D5,D6,D7,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17</t>
   </si>
   <si>
     <t>DO-35_BD2.2-L4.0-D0.50_1N4148</t>
@@ -73,7 +73,7 @@
     <t>CPG151101D06</t>
   </si>
   <si>
-    <t>KEY2,KEY3,KEY4,KEY5,KEY6,KEY7,KEY8,KEY9,KEY10,KEY11,KEY12,KEY13,KEY14,KEY15,KEY16,KEY17</t>
+    <t>KEY0,KEY1,KEY2,KEY3,KEY4,KEY5,KEY6,KEY7,KEY8,KEY9,KEY*,KEY+,KEY-,KEY.,KEY/,KEYENTER</t>
   </si>
   <si>
     <t>KEY-TH_CPG151101D06</t>
@@ -547,7 +547,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
